--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487472_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487472_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>14.5656</v>
+        <v>14.4646</v>
       </c>
       <c r="E2" t="n">
-        <v>11.5189</v>
+        <v>11.5783</v>
       </c>
       <c r="F2" t="n">
-        <v>3.0467</v>
+        <v>2.8864</v>
       </c>
       <c r="G2" t="n">
         <v>8.978300000000001</v>
@@ -610,13 +610,13 @@
         <v>1.3709</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4871</v>
+        <v>0.3861</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1653</v>
+        <v>0.2247</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3218</v>
+        <v>0.1614</v>
       </c>
       <c r="V2" t="n">
         <v>3.9252</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.7993</v>
+        <v>6.4111</v>
       </c>
       <c r="E3" t="n">
-        <v>5.3272</v>
+        <v>5.5648</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4721</v>
+        <v>0.8463000000000001</v>
       </c>
       <c r="G3" t="n">
         <v>3.1244</v>
@@ -688,13 +688,13 @@
         <v>1.9585</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.0509</v>
+        <v>-0.439</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5058</v>
+        <v>-0.2682</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5451</v>
+        <v>-0.1708</v>
       </c>
       <c r="V3" t="n">
         <v>1.7673</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.3593</v>
+        <v>3.5145</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1039</v>
+        <v>-0.1469</v>
       </c>
       <c r="F4" t="n">
-        <v>4.4632</v>
+        <v>3.6613</v>
       </c>
       <c r="G4" t="n">
         <v>4.2213</v>
@@ -766,13 +766,13 @@
         <v>2.7419</v>
       </c>
       <c r="S4" t="n">
-        <v>1.0757</v>
+        <v>0.2308</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4288</v>
+        <v>-0.4717</v>
       </c>
       <c r="U4" t="n">
-        <v>1.5045</v>
+        <v>0.7025</v>
       </c>
       <c r="V4" t="n">
         <v>1.2166</v>
@@ -799,10 +799,10 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3362</v>
+        <v>0.5409</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3485</v>
+        <v>0.5532</v>
       </c>
       <c r="F5" t="n">
         <v>-0.0123</v>
@@ -844,10 +844,10 @@
         <v>0.3917</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1364</v>
+        <v>0.0682</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0594</v>
+        <v>0.1453</v>
       </c>
       <c r="U5" t="n">
         <v>-0.077</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.5303</v>
+        <v>-0.9989</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.514</v>
+        <v>-2.2499</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9837</v>
+        <v>1.251</v>
       </c>
       <c r="G6" t="n">
         <v>-0.9782999999999999</v>
@@ -922,13 +922,13 @@
         <v>1.1751</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3147</v>
+        <v>0.2167</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5764</v>
+        <v>-0.3123</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2617</v>
+        <v>0.529</v>
       </c>
       <c r="V6" t="n">
         <v>-1.2166</v>
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.567</v>
+        <v>-1.3623</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9588</v>
+        <v>-0.7542</v>
       </c>
       <c r="F7" t="n">
         <v>-0.6081</v>
@@ -1000,10 +1000,10 @@
         <v>0.1958</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.077</v>
+        <v>0.1276</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>0.2047</v>
       </c>
       <c r="U7" t="n">
         <v>-0.077</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. GONZALEZ DACAL</t>
+          <t>G. RODRIGUEZ LUQUE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.28</v>
+        <v>-1.5418</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.4244</v>
+        <v>-2.1742</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1444</v>
+        <v>0.6324</v>
       </c>
       <c r="G8" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.2201</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.7179</v>
+        <v>1.8426</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7879</v>
+        <v>-2.0627</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6627999999999999</v>
+        <v>1.3726</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1633</v>
+        <v>3.0623</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4994</v>
+        <v>-1.6896</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5927</v>
+        <v>-1.5927</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8812</v>
+        <v>-1.2197</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2885</v>
+        <v>-0.373</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.5875</v>
+        <v>-0.7834</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.1543</v>
+        <v>-3.917</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5668</v>
+        <v>3.1336</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.7625</v>
+        <v>-0.756</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9328</v>
+        <v>-0.1229</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.8297</v>
+        <v>-0.6331</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.2178</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.4931</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. RODRIGUEZ LUQUE</t>
+          <t>J. GONZALEZ DACAL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.4468</v>
+        <v>-1.6492</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.0258</v>
+        <v>-1.8203</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5789</v>
+        <v>0.1711</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.2201</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>1.8426</v>
+        <v>-0.7179</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.0627</v>
+        <v>0.7879</v>
       </c>
       <c r="J9" t="n">
-        <v>1.3726</v>
+        <v>0.6627999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>3.0623</v>
+        <v>0.1633</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.6896</v>
+        <v>0.4994</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.5927</v>
+        <v>-0.5927</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.2197</v>
+        <v>-0.8812</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.373</v>
+        <v>0.2885</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.7834</v>
+        <v>-0.5875</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.917</v>
+        <v>-2.1543</v>
       </c>
       <c r="R9" t="n">
-        <v>3.1336</v>
+        <v>1.5668</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.6611</v>
+        <v>-1.1317</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9745</v>
+        <v>-0.3288</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6866</v>
+        <v>-0.8028999999999999</v>
       </c>
       <c r="V9" t="n">
-        <v>0.2178</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.4931</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2754</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. NJIE</t>
+          <t>A. BARRIOS UREÑA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.9763</v>
+        <v>-3.2231</v>
       </c>
       <c r="E10" t="n">
-        <v>1.294</v>
+        <v>-2.1522</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.2703</v>
+        <v>-1.0709</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.9875</v>
+        <v>0.2131</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0429</v>
+        <v>1.3699</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.0304</v>
+        <v>-1.1568</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4895</v>
+        <v>1.6818</v>
       </c>
       <c r="K10" t="n">
-        <v>0.4491</v>
+        <v>2.3188</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0404</v>
+        <v>-0.637</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.477</v>
+        <v>-1.4687</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4062</v>
+        <v>-0.9489</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.0708</v>
+        <v>-0.5198</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.1958</v>
+        <v>-1.9585</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9792</v>
+        <v>-4.1128</v>
       </c>
       <c r="R10" t="n">
-        <v>0.7834</v>
+        <v>2.1543</v>
       </c>
       <c r="S10" t="n">
-        <v>1.9695</v>
+        <v>-0.8143</v>
       </c>
       <c r="T10" t="n">
-        <v>2.4496</v>
+        <v>0.0035</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4801</v>
+        <v>-0.8178</v>
       </c>
       <c r="V10" t="n">
-        <v>-3.7625</v>
+        <v>-0.6634</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.6659</v>
+        <v>0.2754</v>
       </c>
       <c r="X10" t="n">
-        <v>-3.0966</v>
+        <v>-0.9387</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. BARRIOS UREÑA</t>
+          <t>A. PACHECO MARTINEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.5781</v>
+        <v>-4.1266</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.3468</v>
+        <v>-1.7602</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.2313</v>
+        <v>-2.3663</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2131</v>
+        <v>-1.0645</v>
       </c>
       <c r="H11" t="n">
-        <v>1.3699</v>
+        <v>0.4512</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.1568</v>
+        <v>-1.5158</v>
       </c>
       <c r="J11" t="n">
-        <v>1.6818</v>
+        <v>-1.4249</v>
       </c>
       <c r="K11" t="n">
-        <v>2.3188</v>
+        <v>0.3793</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.637</v>
+        <v>-1.8042</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.4687</v>
+        <v>0.3603</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.9489</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.5198</v>
+        <v>0.2885</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.9585</v>
+        <v>-0.7834</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.1128</v>
+        <v>-2.1543</v>
       </c>
       <c r="R11" t="n">
-        <v>2.1543</v>
+        <v>1.3709</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1693</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1911</v>
+        <v>0.327</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.9782</v>
+        <v>0.491</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.6634</v>
+        <v>-3.0966</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2754</v>
+        <v>1.492</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.9387</v>
+        <v>-4.5885</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. PACHECO MARTINEZ</t>
+          <t>P. NJIE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.2259</v>
+        <v>-4.3599</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.922</v>
+        <v>-0.06279999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.3039</v>
+        <v>-4.297</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.0645</v>
+        <v>-0.9875</v>
       </c>
       <c r="H12" t="n">
-        <v>0.4512</v>
+        <v>0.0429</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.5158</v>
+        <v>-1.0304</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.4249</v>
+        <v>0.4895</v>
       </c>
       <c r="K12" t="n">
-        <v>0.3793</v>
+        <v>0.4491</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.8042</v>
+        <v>0.0404</v>
       </c>
       <c r="M12" t="n">
-        <v>0.3603</v>
+        <v>-1.477</v>
       </c>
       <c r="N12" t="n">
-        <v>0.07190000000000001</v>
+        <v>-0.4062</v>
       </c>
       <c r="O12" t="n">
-        <v>0.2885</v>
+        <v>-1.0708</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.7834</v>
+        <v>-0.1958</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.1543</v>
+        <v>-0.9792</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3709</v>
+        <v>0.7834</v>
       </c>
       <c r="S12" t="n">
-        <v>0.7186</v>
+        <v>0.5859</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1653</v>
+        <v>1.0928</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5533</v>
+        <v>-0.5068</v>
       </c>
       <c r="V12" t="n">
+        <v>-3.7625</v>
+      </c>
+      <c r="W12" t="n">
+        <v>-0.6659</v>
+      </c>
+      <c r="X12" t="n">
         <v>-3.0966</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.492</v>
-      </c>
-      <c r="X12" t="n">
-        <v>-4.5885</v>
       </c>
     </row>
     <row r="13">
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.455999999999999</v>
+        <v>7.669300000000003</v>
       </c>
       <c r="E13" t="n">
-        <v>5.192899999999999</v>
+        <v>6.575600000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>1.2631</v>
+        <v>1.093900000000001</v>
       </c>
       <c r="G13" t="n">
         <v>12.8413</v>
       </c>
       <c r="H13" t="n">
-        <v>9.628900000000002</v>
+        <v>9.6289</v>
       </c>
       <c r="I13" t="n">
         <v>3.212399999999999</v>
@@ -1450,7 +1450,7 @@
         <v>2.4954</v>
       </c>
       <c r="M13" t="n">
-        <v>-4.827400000000001</v>
+        <v>-4.8274</v>
       </c>
       <c r="N13" t="n">
         <v>-5.5445</v>
@@ -1468,13 +1468,13 @@
         <v>16.8429</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.921</v>
+        <v>-0.7077000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8885999999999996</v>
+        <v>0.4941</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.0324</v>
+        <v>-1.2015</v>
       </c>
       <c r="V13" t="n">
         <v>-1.7224</v>
@@ -1483,13 +1483,13 @@
         <v>7.9979</v>
       </c>
       <c r="X13" t="n">
-        <v>-9.720299999999998</v>
+        <v>-9.7203</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C. LAROUSSE</t>
+          <t>D. SNYERS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.1982</v>
+        <v>1.3355</v>
       </c>
       <c r="E14" t="n">
-        <v>2.2649</v>
+        <v>0.7214</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.0667</v>
+        <v>0.614</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0427</v>
+        <v>1.1975</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5073</v>
+        <v>-1.4043</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4646</v>
+        <v>2.6018</v>
       </c>
       <c r="J14" t="n">
-        <v>2.5967</v>
+        <v>3.7402</v>
       </c>
       <c r="K14" t="n">
-        <v>2.5467</v>
+        <v>0.7706</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0501</v>
+        <v>2.9696</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.5541</v>
+        <v>-2.5427</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.0394</v>
+        <v>-2.1748</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.5145999999999999</v>
+        <v>-0.3678</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.7834</v>
+        <v>0.5875</v>
       </c>
       <c r="Q14" t="n">
         <v>-3.1336</v>
       </c>
       <c r="R14" t="n">
-        <v>2.3502</v>
+        <v>3.7211</v>
       </c>
       <c r="S14" t="n">
-        <v>2.2143</v>
+        <v>0.2163</v>
       </c>
       <c r="T14" t="n">
-        <v>1.3098</v>
+        <v>-0.1029</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9045</v>
+        <v>0.3192</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.2754</v>
+        <v>-0.6659</v>
       </c>
       <c r="W14" t="n">
-        <v>1.492</v>
+        <v>0.2178</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.7673</v>
+        <v>-0.8837</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R. REY ARTIGAS</t>
+          <t>I. LUACES PENIN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.1188</v>
+        <v>1.0561</v>
       </c>
       <c r="E15" t="n">
-        <v>1.3643</v>
+        <v>0.2971</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2455</v>
+        <v>0.7591</v>
       </c>
       <c r="G15" t="n">
-        <v>-3.0623</v>
+        <v>0.431</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.7694</v>
+        <v>-0.0892</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.2929</v>
+        <v>0.5202</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.052</v>
+        <v>0.2873</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.4102</v>
+        <v>0.3181</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.6418</v>
+        <v>-0.0308</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.0104</v>
+        <v>0.1437</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.3593</v>
+        <v>-0.4073</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.6511</v>
+        <v>0.551</v>
       </c>
       <c r="P15" t="n">
-        <v>1.9585</v>
+        <v>0.1958</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R15" t="n">
-        <v>1.9585</v>
+        <v>1.1751</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0648</v>
+        <v>0.0963</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2923</v>
+        <v>-0.2276</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3571</v>
+        <v>0.3239</v>
       </c>
       <c r="V15" t="n">
-        <v>2.1578</v>
+        <v>0.3329</v>
       </c>
       <c r="W15" t="n">
-        <v>2.7086</v>
+        <v>1.2166</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.5507</v>
+        <v>-0.8837</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>I. LUACES PENIN</t>
+          <t>R. REY ARTIGAS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3721</v>
+        <v>1.0211</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.009900000000000001</v>
+        <v>1.1596</v>
       </c>
       <c r="F16" t="n">
-        <v>0.382</v>
+        <v>-0.1385</v>
       </c>
       <c r="G16" t="n">
-        <v>0.431</v>
+        <v>-3.0623</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0892</v>
+        <v>-1.7694</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5202</v>
+        <v>-1.2929</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2873</v>
+        <v>-1.052</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3181</v>
+        <v>-0.4102</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.0308</v>
+        <v>-0.6418</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1437</v>
+        <v>-2.0104</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4073</v>
+        <v>-1.3593</v>
       </c>
       <c r="O16" t="n">
-        <v>0.551</v>
+        <v>-0.6511</v>
       </c>
       <c r="P16" t="n">
-        <v>0.1958</v>
+        <v>1.9585</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1751</v>
+        <v>1.9585</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5877</v>
+        <v>-0.0329</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5346</v>
+        <v>-0.497</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0531</v>
+        <v>0.464</v>
       </c>
       <c r="V16" t="n">
-        <v>0.3329</v>
+        <v>2.1578</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2166</v>
+        <v>2.7086</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.8837</v>
+        <v>-0.5507</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. MARTINEZ GRANDA</t>
+          <t>C. LAROUSSE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2556</v>
+        <v>-0.0011</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7652</v>
+        <v>1.6509</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.0207</v>
+        <v>-1.652</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.6009</v>
+        <v>0.0427</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.7377</v>
+        <v>0.5073</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1368</v>
+        <v>-0.4646</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0157</v>
+        <v>2.5967</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.242</v>
+        <v>2.5467</v>
       </c>
       <c r="L17" t="n">
-        <v>1.2577</v>
+        <v>0.0501</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.6166</v>
+        <v>-2.5541</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.4957</v>
+        <v>-2.0394</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1209</v>
+        <v>-0.5145999999999999</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9792</v>
+        <v>-0.7834</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-3.1336</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9792</v>
+        <v>2.3502</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0245</v>
+        <v>1.015</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5328000000000001</v>
+        <v>0.6958</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5573</v>
+        <v>0.3192</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3905</v>
+        <v>-0.2754</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2166</v>
+        <v>1.492</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.8260999999999999</v>
+        <v>-1.7673</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. SNYERS</t>
+          <t>S. MARTINEZ GRANDA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2991</v>
+        <v>-0.6216</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5066000000000001</v>
+        <v>1.0488</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2075</v>
+        <v>-1.6704</v>
       </c>
       <c r="G18" t="n">
-        <v>1.1975</v>
+        <v>-1.6009</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.4043</v>
+        <v>-2.7377</v>
       </c>
       <c r="I18" t="n">
-        <v>2.6018</v>
+        <v>1.1368</v>
       </c>
       <c r="J18" t="n">
-        <v>3.7402</v>
+        <v>0.0157</v>
       </c>
       <c r="K18" t="n">
-        <v>0.7706</v>
+        <v>-1.242</v>
       </c>
       <c r="L18" t="n">
-        <v>2.9696</v>
+        <v>1.2577</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.5427</v>
+        <v>-1.6166</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.1748</v>
+        <v>-1.4957</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3678</v>
+        <v>-0.1209</v>
       </c>
       <c r="P18" t="n">
-        <v>0.5875</v>
+        <v>0.9792</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.1336</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>3.7211</v>
+        <v>0.9792</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.4183</v>
+        <v>-0.3905</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.331</v>
+        <v>-0.1835</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0873</v>
+        <v>-0.207</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.6659</v>
+        <v>0.3905</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2178</v>
+        <v>1.2166</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.8837</v>
+        <v>-0.8260999999999999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L. SANCHEZ VAZQUEZ</t>
+          <t>S. YUBERO ROSALES</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.3384</v>
+        <v>-0.8793</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8299</v>
+        <v>-1.4455</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5085</v>
+        <v>0.5663</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.9858</v>
+        <v>-0.9056</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.3191</v>
+        <v>-1.3001</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.6667</v>
+        <v>0.3945</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4287</v>
+        <v>0.6423</v>
       </c>
       <c r="K19" t="n">
-        <v>0.4287</v>
+        <v>0.3998</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.2425</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.4145</v>
+        <v>-1.5479</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.7479</v>
+        <v>-1.6999</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6667</v>
+        <v>0.152</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-1.1751</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9792</v>
+        <v>-3.1336</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9792</v>
+        <v>1.9585</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0772</v>
+        <v>0.5931</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2794</v>
+        <v>0.7705</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2021</v>
+        <v>-0.1773</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.2754</v>
+        <v>0.6083</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2754</v>
+        <v>0.3329</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. YUBERO ROSALES</t>
+          <t>G. SABATER MARTINEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.4195</v>
+        <v>-1.0251</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.4455</v>
+        <v>0.8001</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0261</v>
+        <v>-1.8252</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.9056</v>
+        <v>-2.8227</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.3001</v>
+        <v>-2.1005</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3945</v>
+        <v>-0.7223000000000001</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6423</v>
+        <v>-1.3415</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3998</v>
+        <v>-0.7401</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2425</v>
+        <v>-0.6014</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.5479</v>
+        <v>-1.4812</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.6999</v>
+        <v>-1.3603</v>
       </c>
       <c r="O20" t="n">
-        <v>0.152</v>
+        <v>-0.1209</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.1751</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.1336</v>
+        <v>-0.9792</v>
       </c>
       <c r="R20" t="n">
-        <v>1.9585</v>
+        <v>0.9792</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0529</v>
+        <v>-0.1425</v>
       </c>
       <c r="T20" t="n">
-        <v>0.7705</v>
+        <v>0.0794</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7175</v>
+        <v>-0.2219</v>
       </c>
       <c r="V20" t="n">
-        <v>0.6083</v>
+        <v>1.9401</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2754</v>
+        <v>3.0415</v>
       </c>
       <c r="X20" t="n">
-        <v>0.3329</v>
+        <v>-1.1014</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. ROQUE DO VALE CARVAHAL</t>
+          <t>L. SANCHEZ VAZQUEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.5145</v>
+        <v>-1.2628</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1952</v>
+        <v>-0.7276</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.7097</v>
+        <v>-0.5352</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.2235</v>
+        <v>-0.9858</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6104000000000001</v>
+        <v>-0.3191</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.8339</v>
+        <v>-0.6667</v>
       </c>
       <c r="J21" t="n">
-        <v>1.6035</v>
+        <v>0.4287</v>
       </c>
       <c r="K21" t="n">
-        <v>2.9227</v>
+        <v>0.4287</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.3192</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.827</v>
+        <v>-1.4145</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.3123</v>
+        <v>-0.7479</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5145999999999999</v>
+        <v>-0.6667</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.3917</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.1336</v>
+        <v>-0.9792</v>
       </c>
       <c r="R21" t="n">
-        <v>2.7419</v>
+        <v>0.9792</v>
       </c>
       <c r="S21" t="n">
-        <v>1.3173</v>
+        <v>-0.0016</v>
       </c>
       <c r="T21" t="n">
-        <v>0.5087</v>
+        <v>-0.177</v>
       </c>
       <c r="U21" t="n">
-        <v>0.8086</v>
+        <v>0.1754</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.2166</v>
+        <v>-0.2754</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2166</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.4332</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>G. SABATER MARTINEZ</t>
+          <t>P. ROQUE DO VALE CARVAHAL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.6954</v>
+        <v>-1.8261</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1861</v>
+        <v>-0.0095</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.8815</v>
+        <v>-1.8166</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.8227</v>
+        <v>-1.2235</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.1005</v>
+        <v>0.6104000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.7223000000000001</v>
+        <v>-1.8339</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.3415</v>
+        <v>1.6035</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.7401</v>
+        <v>2.9227</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6014</v>
+        <v>-1.3192</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.4812</v>
+        <v>-2.827</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.3603</v>
+        <v>-2.3123</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1209</v>
+        <v>-0.5145999999999999</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>-0.3917</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9792</v>
+        <v>-3.1336</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9792</v>
+        <v>2.7419</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8127</v>
+        <v>1.0057</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5346</v>
+        <v>0.3041</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2781</v>
+        <v>0.7017</v>
       </c>
       <c r="V22" t="n">
-        <v>1.9401</v>
+        <v>-1.2166</v>
       </c>
       <c r="W22" t="n">
-        <v>3.0415</v>
+        <v>1.2166</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.1014</v>
+        <v>-2.4332</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.9178</v>
+        <v>-3.1833</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.4228</v>
+        <v>-3.9344</v>
       </c>
       <c r="F23" t="n">
-        <v>0.505</v>
+        <v>0.7511</v>
       </c>
       <c r="G23" t="n">
         <v>-3.6372</v>
@@ -2248,13 +2248,13 @@
         <v>2.7419</v>
       </c>
       <c r="S23" t="n">
-        <v>1.4061</v>
+        <v>1.1405</v>
       </c>
       <c r="T23" t="n">
-        <v>0.8763</v>
+        <v>0.3646</v>
       </c>
       <c r="U23" t="n">
-        <v>0.5296999999999999</v>
+        <v>0.7759</v>
       </c>
       <c r="V23" t="n">
         <v>-1.2742</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.751200000000001</v>
+        <v>-5.3866</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.4390000000000001</v>
+        <v>-0.4390999999999998</v>
       </c>
       <c r="F24" t="n">
-        <v>-6.311999999999999</v>
+        <v>-4.9474</v>
       </c>
       <c r="G24" t="n">
         <v>-12.5668</v>
@@ -2326,22 +2326,22 @@
         <v>19.5848</v>
       </c>
       <c r="S24" t="n">
-        <v>2.135</v>
+        <v>3.4994</v>
       </c>
       <c r="T24" t="n">
-        <v>1.0262</v>
+        <v>1.0264</v>
       </c>
       <c r="U24" t="n">
-        <v>1.1087</v>
+        <v>2.4731</v>
       </c>
       <c r="V24" t="n">
-        <v>1.722100000000001</v>
+        <v>1.7221</v>
       </c>
       <c r="W24" t="n">
         <v>10.937</v>
       </c>
       <c r="X24" t="n">
-        <v>-9.214700000000001</v>
+        <v>-9.214699999999999</v>
       </c>
     </row>
   </sheetData>
